--- a/output/pdf_financials_xlsx/DCM.xlsx
+++ b/output/pdf_financials_xlsx/DCM.xlsx
@@ -5513,25 +5513,25 @@
         <v>0.183</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>0.242</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>0.254</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>0.173</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>0.207</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>0.177</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>0.307</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="92">
@@ -10934,7 +10934,11 @@
           <t>Translation reserve</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -14578,7 +14582,11 @@
           <t>Translation reserve</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DCM.xlsx
+++ b/output/pdf_financials_xlsx/DCM.xlsx
@@ -1020,28 +1020,28 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.074</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.021</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.011</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1965,28 +1965,28 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>4.231</v>
+        <v>4.331</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>7.984</v>
+        <v>8.058</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-37.135</v>
+        <v>-37.12</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-46.358</v>
+        <v>-46.343</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>6.227</v>
+        <v>6.248</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-18.443</v>
+        <v>-18.432</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-32.184</v>
+        <v>-32.176</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-7.915</v>
+        <v>-7.909</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>3.372</v>
@@ -2079,28 +2079,28 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>4.231</v>
+        <v>4.331</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>18.259</v>
+        <v>18.333</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-27.893</v>
+        <v>-27.878</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-37.988</v>
+        <v>-37.973</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>8.143000000000001</v>
+        <v>8.164</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-16.494</v>
+        <v>-16.483</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-30.092</v>
+        <v>-30.084</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-4.406</v>
+        <v>-4.4</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>7.545</v>
@@ -2136,28 +2136,28 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1.27343484293501</v>
+        <v>1.30353257025562</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>5.498986577039721</v>
+        <v>5.521272847191478</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-8.293712739544771</v>
+        <v>-8.289252635178331</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-11.98507071847956</v>
+        <v>-11.98033827505592</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>2.600143689630398</v>
+        <v>2.606849205715654</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-5.415414922432898</v>
+        <v>-5.411803332512517</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-10.81034476564773</v>
+        <v>-10.80747082047542</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-1.521781928580557</v>
+        <v>-1.519709597311496</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>2.337585084069412</v>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>4.192</v>
+        <v>6.277</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>4.819</v>
@@ -3091,7 +3091,7 @@
         <v>4.404</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.929</v>
+        <v>4.103</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>5.587</v>
@@ -3112,19 +3112,19 @@
         <v>2.611</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.58</v>
+        <v>3.44</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.984</v>
+        <v>2.999</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>5.313</v>
+        <v>16.603</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>5.989</v>
+        <v>9.420999999999999</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>4.899</v>
+        <v>5.144</v>
       </c>
     </row>
     <row r="49">
@@ -7319,40 +7319,40 @@
         <v>0</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.017</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.027</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.037</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.018</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-2.43</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-10.904</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-11.202</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-8.73</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-6.315</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-7.812</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-7.455</v>
       </c>
     </row>
     <row r="125">
@@ -7376,40 +7376,40 @@
         <v>0</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.017</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.027</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.037</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.018</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-2.43</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-10.904</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-11.202</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-8.73</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-6.315</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-7.812</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-7.455</v>
       </c>
     </row>
     <row r="126">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
@@ -41128,7 +41128,11 @@
           <t>Principal portion of lease payments (note 12)</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -44326,7 +44330,11 @@
           <t>Lease payments (note 12)</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E391" t="inlineStr">
         <is>
           <t>-</t>
@@ -46980,7 +46988,11 @@
           <t>Lease payments (note 11)</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -53032,7 +53044,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E484" t="inlineStr">
         <is>
           <t>-</t>
@@ -68436,7 +68452,11 @@
           <t>General and administration expenses</t>
         </is>
       </c>
-      <c r="D648" t="inlineStr"/>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E648" t="inlineStr">
         <is>
           <t>-</t>
@@ -71470,7 +71490,11 @@
           <t>General and administration expenses</t>
         </is>
       </c>
-      <c r="D681" t="inlineStr"/>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E681" t="inlineStr">
         <is>
           <t>-</t>
@@ -77400,7 +77424,7 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
@@ -77496,7 +77520,7 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
@@ -78994,7 +79018,11 @@
           <t>General and administration expenses</t>
         </is>
       </c>
-      <c r="D761" t="inlineStr"/>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E761" t="inlineStr">
         <is>
           <t>-</t>
@@ -80798,7 +80826,7 @@
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E780" t="inlineStr">
@@ -80890,7 +80918,7 @@
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">

--- a/output/pdf_financials_xlsx/DCM.xlsx
+++ b/output/pdf_financials_xlsx/DCM.xlsx
@@ -2022,49 +2022,49 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>6.232</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>10.275</v>
+        <v>16.027</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>9.242000000000001</v>
+        <v>35.888</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>8.369999999999999</v>
+        <v>32.059</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1.916</v>
+        <v>23.828</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>1.949</v>
+        <v>6.703</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.092</v>
+        <v>6.144</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3.509</v>
+        <v>7.652</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>4.173</v>
+        <v>8.851000000000001</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>3.962</v>
+        <v>16.861</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>3.589</v>
+        <v>15.15</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.606</v>
+        <v>11.18</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>2.881</v>
+        <v>21.723</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>2.011</v>
+        <v>26.249</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>1.342</v>
+        <v>28.02</v>
       </c>
     </row>
     <row r="29">
@@ -2079,49 +2079,49 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>4.331</v>
+        <v>10.563</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>18.333</v>
+        <v>24.085</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-27.878</v>
+        <v>-1.232</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-37.973</v>
+        <v>-14.284</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>8.164</v>
+        <v>30.076</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-16.483</v>
+        <v>-11.729</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-30.084</v>
+        <v>-26.032</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-4.4</v>
+        <v>-0.257</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>7.545</v>
+        <v>12.223</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-10.982</v>
+        <v>1.917</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>8.754</v>
+        <v>20.315</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>23.724</v>
+        <v>33.298</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-12.557</v>
+        <v>6.285</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>19.788</v>
+        <v>44.026</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>25.885</v>
+        <v>52.563</v>
       </c>
     </row>
     <row r="30">
@@ -2136,49 +2136,49 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1.30353257025562</v>
+        <v>3.179222936876037</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>5.521272847191478</v>
+        <v>7.253578602771328</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-8.289252635178331</v>
+        <v>-0.3663232386304506</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-11.98033827505592</v>
+        <v>-4.506548124217176</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>2.606849205715654</v>
+        <v>9.603576275245469</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-5.411803332512517</v>
+        <v>-3.85093983419519</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-10.80747082047542</v>
+        <v>-9.351817590699914</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-1.519709597311496</v>
+        <v>-0.08876485602478508</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>2.337585084069412</v>
+        <v>3.78691881810211</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-3.882266434762935</v>
+        <v>0.6776820939210113</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>3.719866910861722</v>
+        <v>8.632521852199668</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>8.664592190033748</v>
+        <v>12.16125403573359</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-2.804623373722709</v>
+        <v>1.403763470880563</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>4.12287793047696</v>
+        <v>9.172924184716932</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>5.747649647613676</v>
+        <v>11.67138143432558</v>
       </c>
     </row>
     <row r="31">
@@ -5940,49 +5940,49 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>6.232</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>16.027</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>14.969</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>13.7</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>6.856</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>6.703</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>6.144</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>7.652</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>8.851000000000001</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>16.861</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>15.15</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>11.18</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>21.723</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>26.249</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>28.02</v>
       </c>
     </row>
     <row r="101">
@@ -6624,46 +6624,46 @@
         </is>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>2.085</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.654</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.638</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>1.282</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.845</v>
       </c>
       <c r="Q112" s="3" t="n">
         <v>0</v>
@@ -37622,7 +37622,11 @@
           <t>Depreciation of property, plant and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>
@@ -37714,7 +37718,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -37806,7 +37810,11 @@
           <t>Depreciation of right-of-use-assets (note 8)</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -40122,7 +40130,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
@@ -44614,7 +44626,11 @@
           <t>Depreciation of property, plant and equipment (note 6)</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -44710,7 +44726,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -44806,7 +44822,11 @@
           <t>Depreciation of right-of-use-assets (note 7)</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -47544,7 +47564,11 @@
           <t>Depreciation of property, plant and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>
@@ -47640,7 +47664,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -47736,7 +47760,11 @@
           <t>Depreciation of right-of-use-assets (note 8)</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -50644,7 +50672,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E458" t="inlineStr">
         <is>
           <t>-</t>
@@ -50736,7 +50768,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -53686,7 +53718,11 @@
           <t>Depreciation of property, plant and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E491" t="inlineStr">
         <is>
           <t>-</t>
@@ -53782,7 +53818,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
@@ -56496,7 +56532,11 @@
           <t>Depreciation of property, plant and equipment (note 6)</t>
         </is>
       </c>
-      <c r="D521" t="inlineStr"/>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E521" t="inlineStr">
         <is>
           <t>-</t>
@@ -56592,7 +56632,7 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -58380,7 +58420,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E541" t="inlineStr">
         <is>
           <t>-</t>
@@ -58472,7 +58516,7 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -62158,7 +62202,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D581" t="inlineStr"/>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E581" t="inlineStr">
         <is>
           <t>-</t>
@@ -62254,7 +62302,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
@@ -65368,7 +65416,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D615" t="inlineStr"/>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E615" t="inlineStr">
         <is>
           <t>-</t>
@@ -80154,7 +80206,11 @@
           <t>General and administration expenses excluding amortization of intangible assets</t>
         </is>
       </c>
-      <c r="D773" t="inlineStr"/>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E773" t="inlineStr">
         <is>
           <t>-</t>
@@ -80536,7 +80592,7 @@
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
@@ -82056,7 +82112,11 @@
           <t>General and administration expenses excluding amortization of intangible assets</t>
         </is>
       </c>
-      <c r="D793" t="inlineStr"/>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E793" t="inlineStr">
         <is>
           <t>-</t>
@@ -82534,7 +82594,7 @@
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">

--- a/output/pdf_financials_xlsx/DCM.xlsx
+++ b/output/pdf_financials_xlsx/DCM.xlsx
@@ -3551,52 +3551,52 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>0</v>
+        <v>58.598</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>60.44</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>62.904</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>64.779</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>65.985</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>68.655</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>68.79900000000001</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>64.059</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>60.405</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>60.847</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>52.384</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0</v>
+        <v>79.995</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0</v>
+        <v>86.158</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0</v>
+        <v>87.56100000000001</v>
       </c>
     </row>
     <row r="57">
@@ -3606,52 +3606,52 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>0</v>
+        <v>27.926</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>34.42</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>38.755</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>44.359</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>48.719</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>53.132</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>54.377</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>52.867</v>
       </c>
       <c r="J57" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>47.255</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0</v>
+        <v>47.343</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>0</v>
+        <v>52.431</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>0</v>
+        <v>45.605</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>0</v>
+        <v>49.637</v>
       </c>
       <c r="P57" s="3" t="n">
-        <v>0</v>
+        <v>51.346</v>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>0</v>
+        <v>55.516</v>
       </c>
     </row>
     <row r="58">
@@ -6357,31 +6357,31 @@
         <v>0</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>0.779</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>0.473</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>0.488</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>0.328</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>0.675</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="108">
@@ -6858,43 +6858,43 @@
         <v>0</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.415</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.007</v>
       </c>
       <c r="G116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.302</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.432</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-3.375</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-5.111</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-3.878</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-1.39</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-0.127</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0</v>
+        <v>-0.132</v>
       </c>
     </row>
     <row r="117">
@@ -7064,10 +7064,8 @@
       <c r="P119" s="3" t="n">
         <v>-10.075</v>
       </c>
-      <c r="Q119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q119" s="3" t="n">
+        <v>2.087</v>
       </c>
     </row>
     <row r="120">
@@ -7181,7 +7179,7 @@
         <v>0</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>0</v>
+        <v>-0.966</v>
       </c>
     </row>
     <row r="122">
@@ -8011,15 +8009,13 @@
         <v>21.2</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>21.534</v>
+        <v>21.575</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>12.483</v>
-      </c>
-      <c r="Q135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>12.433</v>
+      </c>
+      <c r="Q135" s="3" t="n">
+        <v>20.828</v>
       </c>
     </row>
   </sheetData>
@@ -37904,7 +37900,11 @@
           <t>Share-based compensation expense (note 17)</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -39674,7 +39674,11 @@
           <t>Total cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -40044,7 +40048,11 @@
           <t>Purchase of intangible assets (note 9)</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -41044,7 +41052,11 @@
           <t>Repurchases of shares</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -43960,7 +43972,11 @@
           <t>Total cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -46250,7 +46266,11 @@
           <t>Total cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -46438,7 +46458,11 @@
           <t>Purchase of intangible assets (note 8)</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
           <t>-</t>
@@ -47956,7 +47980,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
           <t>-</t>
@@ -50860,7 +50888,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
@@ -52428,7 +52460,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
           <t>-</t>
@@ -53914,7 +53950,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
           <t>-</t>
@@ -57572,7 +57612,11 @@
           <t>Purchase of intangible assets (note 7)</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E532" t="inlineStr">
         <is>
           <t>-</t>
@@ -72374,7 +72418,11 @@
           <t>INCOME TAX (RECOVERY) EXPENSE total</t>
         </is>
       </c>
-      <c r="D690" t="inlineStr"/>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E690" t="inlineStr">
         <is>
           <t>-</t>
